--- a/data/grafik-sanrazryva-2026-12.xlsx
+++ b/data/grafik-sanrazryva-2026-12.xlsx
@@ -1603,7 +1603,11 @@
       <c r="AD23" s="4" t="n"/>
       <c r="AE23" s="4" t="n"/>
       <c r="AF23" s="4" t="n"/>
-      <c r="AG23" s="4" t="n"/>
+      <c r="AG23" s="5" t="inlineStr">
+        <is>
+          <t>ОС/ОЧН</t>
+        </is>
+      </c>
       <c r="AH23" s="4" t="n">
         <v>1</v>
       </c>
@@ -4217,65 +4221,65 @@
         <v>1</v>
       </c>
       <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ПН</t>
-        </is>
-      </c>
-      <c r="K70" s="4" t="n"/>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="n"/>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
+          <t>СО</t>
         </is>
       </c>
       <c r="N70" s="4" t="n"/>
-      <c r="O70" s="4" t="inlineStr">
-        <is>
-          <t>СО</t>
-        </is>
-      </c>
-      <c r="P70" s="4" t="n"/>
-      <c r="Q70" s="8" t="inlineStr">
+      <c r="O70" s="8" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="R70" s="7" t="inlineStr">
+      <c r="P70" s="7" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="Q70" s="4" t="n"/>
+      <c r="R70" s="4" t="n"/>
       <c r="S70" s="4" t="n"/>
       <c r="T70" s="4" t="n"/>
       <c r="U70" s="4" t="n"/>
@@ -4306,65 +4310,65 @@
         <v>2</v>
       </c>
       <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ПН</t>
-        </is>
-      </c>
-      <c r="K71" s="4" t="n"/>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="n"/>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
+          <t>СО</t>
         </is>
       </c>
       <c r="N71" s="4" t="n"/>
-      <c r="O71" s="4" t="inlineStr">
-        <is>
-          <t>СО</t>
-        </is>
-      </c>
-      <c r="P71" s="4" t="n"/>
-      <c r="Q71" s="8" t="inlineStr">
+      <c r="O71" s="8" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="R71" s="7" t="inlineStr">
+      <c r="P71" s="7" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="Q71" s="4" t="n"/>
+      <c r="R71" s="4" t="n"/>
       <c r="S71" s="4" t="n"/>
       <c r="T71" s="4" t="n"/>
       <c r="U71" s="4" t="n"/>
@@ -4392,65 +4396,65 @@
       </c>
       <c r="C72" s="4" t="n"/>
       <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="n"/>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ПН</t>
-        </is>
-      </c>
-      <c r="L72" s="4" t="n"/>
-      <c r="M72" s="4" t="inlineStr">
-        <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="n"/>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
+          <t>СО</t>
         </is>
       </c>
       <c r="O72" s="4" t="n"/>
-      <c r="P72" s="4" t="inlineStr">
-        <is>
-          <t>СО</t>
-        </is>
-      </c>
-      <c r="Q72" s="4" t="n"/>
-      <c r="R72" s="8" t="inlineStr">
+      <c r="P72" s="8" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="S72" s="7" t="inlineStr">
+      <c r="Q72" s="7" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="R72" s="4" t="n"/>
+      <c r="S72" s="4" t="n"/>
       <c r="T72" s="4" t="n"/>
       <c r="U72" s="4" t="n"/>
       <c r="V72" s="4" t="n"/>
@@ -4477,65 +4481,65 @@
       </c>
       <c r="C73" s="4" t="n"/>
       <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ПН</t>
-        </is>
-      </c>
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="inlineStr">
-        <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
+          <t>СО</t>
         </is>
       </c>
       <c r="O73" s="4" t="n"/>
-      <c r="P73" s="4" t="inlineStr">
-        <is>
-          <t>СО</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="n"/>
-      <c r="R73" s="8" t="inlineStr">
+      <c r="P73" s="8" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="S73" s="7" t="inlineStr">
+      <c r="Q73" s="7" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="R73" s="4" t="n"/>
+      <c r="S73" s="4" t="n"/>
       <c r="T73" s="4" t="n"/>
       <c r="U73" s="4" t="n"/>
       <c r="V73" s="4" t="n"/>
@@ -4563,65 +4567,65 @@
       <c r="C74" s="4" t="n"/>
       <c r="D74" s="4" t="n"/>
       <c r="E74" s="4" t="n"/>
-      <c r="F74" s="4" t="n"/>
-      <c r="G74" s="5" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="H74" s="6" t="inlineStr">
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ПН</t>
-        </is>
-      </c>
-      <c r="M74" s="4" t="n"/>
-      <c r="N74" s="4" t="inlineStr">
-        <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
+          <t>СО</t>
         </is>
       </c>
       <c r="P74" s="4" t="n"/>
-      <c r="Q74" s="4" t="inlineStr">
-        <is>
-          <t>СО</t>
-        </is>
-      </c>
-      <c r="R74" s="4" t="n"/>
-      <c r="S74" s="8" t="inlineStr">
+      <c r="Q74" s="8" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="T74" s="7" t="inlineStr">
+      <c r="R74" s="7" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="S74" s="4" t="n"/>
+      <c r="T74" s="4" t="n"/>
       <c r="U74" s="4" t="n"/>
       <c r="V74" s="4" t="n"/>
       <c r="W74" s="4" t="n"/>
@@ -4648,65 +4652,65 @@
       <c r="C75" s="4" t="n"/>
       <c r="D75" s="4" t="n"/>
       <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="n"/>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ПН</t>
-        </is>
-      </c>
-      <c r="M75" s="4" t="n"/>
-      <c r="N75" s="4" t="inlineStr">
-        <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="n"/>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
+          <t>СО</t>
         </is>
       </c>
       <c r="P75" s="4" t="n"/>
-      <c r="Q75" s="4" t="inlineStr">
-        <is>
-          <t>СО</t>
-        </is>
-      </c>
-      <c r="R75" s="4" t="n"/>
-      <c r="S75" s="8" t="inlineStr">
+      <c r="Q75" s="8" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="T75" s="7" t="inlineStr">
+      <c r="R75" s="7" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="S75" s="4" t="n"/>
+      <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
@@ -4734,65 +4738,65 @@
       <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
-      <c r="G76" s="4" t="n"/>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="I76" s="6" t="inlineStr">
+      <c r="H76" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ПН</t>
-        </is>
-      </c>
-      <c r="N76" s="4" t="n"/>
-      <c r="O76" s="4" t="inlineStr">
-        <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
+          <t>СО</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
-      <c r="R76" s="4" t="inlineStr">
-        <is>
-          <t>СО</t>
-        </is>
-      </c>
-      <c r="S76" s="4" t="n"/>
-      <c r="T76" s="8" t="inlineStr">
+      <c r="R76" s="8" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="U76" s="7" t="inlineStr">
+      <c r="S76" s="7" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="T76" s="4" t="n"/>
+      <c r="U76" s="4" t="n"/>
       <c r="V76" s="4" t="n"/>
       <c r="W76" s="4" t="n"/>
       <c r="X76" s="4" t="n"/>
@@ -4819,65 +4823,65 @@
       <c r="D77" s="4" t="n"/>
       <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="n"/>
-      <c r="G77" s="4" t="n"/>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="H77" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ПН</t>
-        </is>
-      </c>
-      <c r="N77" s="4" t="n"/>
-      <c r="O77" s="4" t="inlineStr">
-        <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="O77" s="4" t="n"/>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
+          <t>СО</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
-      <c r="R77" s="4" t="inlineStr">
-        <is>
-          <t>СО</t>
-        </is>
-      </c>
-      <c r="S77" s="4" t="n"/>
-      <c r="T77" s="8" t="inlineStr">
+      <c r="R77" s="8" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="U77" s="7" t="inlineStr">
+      <c r="S77" s="7" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="T77" s="4" t="n"/>
+      <c r="U77" s="4" t="n"/>
       <c r="V77" s="4" t="n"/>
       <c r="W77" s="4" t="n"/>
       <c r="X77" s="4" t="n"/>
@@ -4905,65 +4909,65 @@
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
       <c r="G78" s="4" t="n"/>
-      <c r="H78" s="4" t="n"/>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="J78" s="6" t="inlineStr">
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ПН</t>
-        </is>
-      </c>
-      <c r="O78" s="4" t="n"/>
-      <c r="P78" s="4" t="inlineStr">
-        <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
+          <t>СО</t>
         </is>
       </c>
       <c r="R78" s="4" t="n"/>
-      <c r="S78" s="4" t="inlineStr">
-        <is>
-          <t>СО</t>
-        </is>
-      </c>
-      <c r="T78" s="4" t="n"/>
-      <c r="U78" s="8" t="inlineStr">
+      <c r="S78" s="8" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="V78" s="7" t="inlineStr">
+      <c r="T78" s="7" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="U78" s="4" t="n"/>
+      <c r="V78" s="4" t="n"/>
       <c r="W78" s="4" t="n"/>
       <c r="X78" s="4" t="n"/>
       <c r="Y78" s="4" t="n"/>
@@ -4990,65 +4994,65 @@
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
-      <c r="H79" s="4" t="n"/>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="J79" s="6" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ПН</t>
-        </is>
-      </c>
-      <c r="O79" s="4" t="n"/>
-      <c r="P79" s="4" t="inlineStr">
-        <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
+          <t>СО</t>
         </is>
       </c>
       <c r="R79" s="4" t="n"/>
-      <c r="S79" s="4" t="inlineStr">
-        <is>
-          <t>СО</t>
-        </is>
-      </c>
-      <c r="T79" s="4" t="n"/>
-      <c r="U79" s="8" t="inlineStr">
+      <c r="S79" s="8" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="V79" s="7" t="inlineStr">
+      <c r="T79" s="7" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="U79" s="4" t="n"/>
+      <c r="V79" s="4" t="n"/>
       <c r="W79" s="4" t="n"/>
       <c r="X79" s="4" t="n"/>
       <c r="Y79" s="4" t="n"/>
@@ -5076,65 +5080,65 @@
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
       <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="n"/>
-      <c r="J80" s="5" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="K80" s="6" t="inlineStr">
+      <c r="J80" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ПН</t>
-        </is>
-      </c>
-      <c r="P80" s="4" t="n"/>
-      <c r="Q80" s="4" t="inlineStr">
-        <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="P80" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="n"/>
       <c r="R80" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
+          <t>СО</t>
         </is>
       </c>
       <c r="S80" s="4" t="n"/>
-      <c r="T80" s="4" t="inlineStr">
-        <is>
-          <t>СО</t>
-        </is>
-      </c>
-      <c r="U80" s="4" t="n"/>
-      <c r="V80" s="8" t="inlineStr">
+      <c r="T80" s="8" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="W80" s="7" t="inlineStr">
+      <c r="U80" s="7" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="V80" s="4" t="n"/>
+      <c r="W80" s="4" t="n"/>
       <c r="X80" s="4" t="n"/>
       <c r="Y80" s="4" t="n"/>
       <c r="Z80" s="4" t="n"/>
@@ -5161,65 +5165,65 @@
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
-      <c r="J81" s="5" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>ОС/ОЧН</t>
         </is>
       </c>
-      <c r="K81" s="6" t="inlineStr">
+      <c r="J81" s="6" t="inlineStr">
         <is>
           <t>МС</t>
         </is>
       </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>ПР/Р</t>
+        </is>
+      </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>ПР/Р</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>Р</t>
+          <t>Р\ДС</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>Р\ДС</t>
+          <t>ДЗ/ПН</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>ДЗ/ПН</t>
-        </is>
-      </c>
-      <c r="P81" s="4" t="n"/>
-      <c r="Q81" s="4" t="inlineStr">
-        <is>
-          <t>ЗО/ДЗ/ГГ/СО</t>
-        </is>
-      </c>
+          <t>ЗО/ДЗ/ГГ</t>
+        </is>
+      </c>
+      <c r="P81" s="4" t="inlineStr">
+        <is>
+          <t>ГФ</t>
+        </is>
+      </c>
+      <c r="Q81" s="4" t="n"/>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>ГФ</t>
+          <t>СО</t>
         </is>
       </c>
       <c r="S81" s="4" t="n"/>
-      <c r="T81" s="4" t="inlineStr">
-        <is>
-          <t>СО</t>
-        </is>
-      </c>
-      <c r="U81" s="4" t="n"/>
-      <c r="V81" s="8" t="inlineStr">
+      <c r="T81" s="8" t="inlineStr">
         <is>
           <t>ПДГ/ОД</t>
         </is>
       </c>
-      <c r="W81" s="7" t="inlineStr">
+      <c r="U81" s="7" t="inlineStr">
         <is>
           <t>ЗС</t>
         </is>
       </c>
+      <c r="V81" s="4" t="n"/>
+      <c r="W81" s="4" t="n"/>
       <c r="X81" s="4" t="n"/>
       <c r="Y81" s="4" t="n"/>
       <c r="Z81" s="4" t="n"/>
